--- a/VFC.xlsx
+++ b/VFC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6633A9-6B36-4FF6-88F0-C4F635A9C3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D8E787-575E-4D3E-987D-B7DD50DC8793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{FD9221D3-9194-474F-AA6F-D3A3CA930557}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>VF Corporation</t>
   </si>
@@ -165,24 +165,6 @@
     <t>Brands:</t>
   </si>
   <si>
-    <t>Vans, The North Face, Timberland, Dickies, Altra, Eastpak</t>
-  </si>
-  <si>
-    <t>Icebreaker, Jansport, Kipling, Napapijri, Smartwool</t>
-  </si>
-  <si>
-    <t>North Face Revenue</t>
-  </si>
-  <si>
-    <t>Vans Revenue</t>
-  </si>
-  <si>
-    <t>Timberland Revenue</t>
-  </si>
-  <si>
-    <t>Dickies Revenue</t>
-  </si>
-  <si>
     <t>Other Revenue</t>
   </si>
   <si>
@@ -213,7 +195,31 @@
     <t>Tax Rate</t>
   </si>
   <si>
-    <t>FQ326</t>
+    <t>FQ426</t>
+  </si>
+  <si>
+    <t>The North Face, Timberland, Vans, Kipling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastpack, JanSport, Dickies, Altra, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smartwool, Napapijri, Icebreaker </t>
+  </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>FY26</t>
+  </si>
+  <si>
+    <t>FY24</t>
+  </si>
+  <si>
+    <t>Outdoor Revenue</t>
+  </si>
+  <si>
+    <t>Actuve Revenue</t>
   </si>
 </sst>
 </file>
@@ -333,9 +339,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -672,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406E3357-E065-4428-904F-B44A426A31A2}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="2" customWidth="1"/>
@@ -692,7 +696,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="2">
-        <v>20.3</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -700,10 +704,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="3">
-        <v>391.26334300000002</v>
+        <v>391.76970499999999</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -715,7 +719,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>7942.6458629000008</v>
+        <v>6550.3894675999991</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -726,10 +730,10 @@
         <v>7</v>
       </c>
       <c r="H5" s="3">
-        <v>1466.4690000000001</v>
+        <v>823.94299999999998</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -737,11 +741,11 @@
         <v>8</v>
       </c>
       <c r="H6" s="3">
-        <f>10.522+588.196+3556.932</f>
-        <v>4155.6499999999996</v>
+        <f>10.139+3519.87</f>
+        <v>3530.009</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -750,7 +754,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>10631.826862900001</v>
+        <v>9256.4554675999989</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -764,13 +768,18 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>42</v>
+      <c r="B12" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>43</v>
+      <c r="B13" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="15" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +792,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC6FD6D1-E9FA-4061-9239-71EF4FDE7FAB}">
-  <dimension ref="A1:GY254"/>
+  <dimension ref="A1:GY252"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -822,16 +831,25 @@
         <v>18</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:207" x14ac:dyDescent="0.2">
@@ -869,9 +887,15 @@
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
+      <c r="P3" s="7">
+        <v>5152.7579999999998</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>4833.5249999999996</v>
+      </c>
+      <c r="R3" s="7">
+        <v>4830.0940000000001</v>
+      </c>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -977,9 +1001,15 @@
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
+      <c r="P4" s="7">
+        <v>3339.6559999999999</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>3248.4609999999998</v>
+      </c>
+      <c r="R4" s="7">
+        <v>3371.92</v>
+      </c>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
@@ -1085,9 +1115,15 @@
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
+      <c r="P5" s="7">
+        <v>1403.2639999999999</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>1422.7049999999999</v>
+      </c>
+      <c r="R5" s="7">
+        <v>1403.193</v>
+      </c>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
@@ -1159,39 +1195,31 @@
       <c r="CI5" s="7"/>
     </row>
     <row r="6" spans="1:207" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>44</v>
+      <c r="B6" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="7">
-        <v>814.3</v>
-      </c>
-      <c r="G6" s="7">
-        <v>524.20000000000005</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1091.4000000000001</v>
-      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="7">
-        <v>834.5</v>
-      </c>
-      <c r="K6" s="7">
-        <v>557.4</v>
-      </c>
-      <c r="L6" s="7">
-        <v>1157.0999999999999</v>
-      </c>
-      <c r="M6" s="7">
-        <v>1356.3</v>
-      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
+      <c r="P6" s="7">
+        <v>5230.2870000000003</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>5311.0609999999997</v>
+      </c>
+      <c r="R6" s="7">
+        <v>5741.7920000000004</v>
+      </c>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
       <c r="U6" s="7"/>
@@ -1263,39 +1291,31 @@
       <c r="CI6" s="7"/>
     </row>
     <row r="7" spans="1:207" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>45</v>
+      <c r="B7" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="7">
-        <v>631.20000000000005</v>
-      </c>
-      <c r="G7" s="7">
-        <v>581.79999999999995</v>
-      </c>
-      <c r="H7" s="7">
-        <v>667.4</v>
-      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="7">
-        <v>492.6</v>
-      </c>
-      <c r="K7" s="7">
-        <v>498</v>
-      </c>
-      <c r="L7" s="7">
-        <v>606.9</v>
-      </c>
-      <c r="M7" s="7">
-        <v>557.6</v>
-      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
+      <c r="P7" s="7">
+        <v>3327.6120000000001</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>2914.3069999999998</v>
+      </c>
+      <c r="R7" s="7">
+        <v>2720.9670000000001</v>
+      </c>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
@@ -1368,38 +1388,42 @@
     </row>
     <row r="8" spans="1:207" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7">
-        <v>341.5</v>
+        <v>297.89999999999998</v>
       </c>
-      <c r="G8" s="7">
-        <v>229.4</v>
-      </c>
-      <c r="H8" s="7">
-        <v>475.3</v>
+      <c r="G8" s="7"/>
+      <c r="H8" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7">
-        <v>376</v>
+        <v>301.5</v>
       </c>
-      <c r="K8" s="7">
-        <v>255.1</v>
+      <c r="K8" s="10" t="s">
+        <v>47</v>
       </c>
-      <c r="L8" s="7">
-        <v>506.4</v>
+      <c r="L8" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="M8" s="7">
-        <v>469.7</v>
+        <v>392.2</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
+      <c r="P8" s="7">
+        <v>1357.779</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>1279.3230000000001</v>
+      </c>
+      <c r="R8" s="7">
+        <v>1142.4480000000001</v>
+      </c>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
       <c r="U8" s="7"/>
@@ -1472,36 +1496,48 @@
     </row>
     <row r="9" spans="1:207" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7">
+        <v>1156.502</v>
+      </c>
       <c r="F9" s="7">
-        <v>162.4</v>
+        <v>967.6</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="10" t="s">
-        <v>53</v>
+      <c r="G9" s="7">
+        <v>1013.774</v>
       </c>
-      <c r="I9" s="7"/>
+      <c r="H9" s="7">
+        <v>1827.796</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1250.9369999999999</v>
+      </c>
       <c r="J9" s="7">
-        <v>139.30000000000001</v>
+        <v>920.8</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>53</v>
+      <c r="K9" s="7">
+        <v>1024.5060000000001</v>
       </c>
-      <c r="L9" s="10" t="s">
-        <v>53</v>
+      <c r="L9" s="7">
+        <v>1876.9469999999999</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>53</v>
+      <c r="M9" s="7">
+        <v>1237.443</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
+      <c r="P9" s="7">
+        <v>5422.0169999999998</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>5300.0940000000001</v>
+      </c>
+      <c r="R9" s="7">
+        <v>5343.643</v>
+      </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
@@ -1574,36 +1610,48 @@
     </row>
     <row r="10" spans="1:207" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="7">
+        <v>1606.1969999999999</v>
+      </c>
       <c r="F10" s="7">
-        <v>297.89999999999998</v>
+        <v>1279.7</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="10" t="s">
-        <v>53</v>
+      <c r="G10" s="7">
+        <v>740.95500000000004</v>
       </c>
-      <c r="I10" s="7"/>
+      <c r="H10" s="7">
+        <v>914.93700000000001</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1565.569</v>
+      </c>
       <c r="J10" s="7">
-        <v>301.5</v>
+        <v>1223</v>
       </c>
-      <c r="K10" s="10" t="s">
-        <v>53</v>
+      <c r="K10" s="7">
+        <v>720.66300000000001</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>53</v>
+      <c r="L10" s="7">
+        <v>909.86099999999999</v>
       </c>
       <c r="M10" s="7">
-        <v>392.2</v>
+        <v>1626.002</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
+      <c r="P10" s="7">
+        <v>4426.5879999999997</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>4142.2749999999996</v>
+      </c>
+      <c r="R10" s="7">
+        <v>4211.8689999999997</v>
+      </c>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
@@ -1676,42 +1724,48 @@
     </row>
     <row r="11" spans="1:207" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7">
-        <v>1156.502</v>
+        <v>17.495000000000001</v>
       </c>
       <c r="F11" s="7">
-        <v>967.6</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7">
-        <v>1013.774</v>
+        <v>14.331</v>
       </c>
       <c r="H11" s="7">
-        <v>1827.796</v>
+        <v>15.215</v>
       </c>
       <c r="I11" s="7">
-        <v>1250.9369999999999</v>
+        <v>17.405999999999999</v>
       </c>
       <c r="J11" s="7">
-        <v>920.8</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7">
-        <v>1024.5060000000001</v>
+        <v>15.497</v>
       </c>
       <c r="L11" s="7">
-        <v>1876.9469999999999</v>
+        <v>15.898</v>
       </c>
       <c r="M11" s="7">
-        <v>1237.443</v>
+        <v>12.356</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
+      <c r="P11" s="7">
+        <v>67.072999999999993</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>62.322000000000003</v>
+      </c>
+      <c r="R11" s="7">
+        <v>49.695</v>
+      </c>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
@@ -1783,43 +1837,49 @@
       <c r="CI11" s="7"/>
     </row>
     <row r="12" spans="1:207" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>35</v>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7">
-        <v>1606.1969999999999</v>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
+        <v>2780.194</v>
       </c>
-      <c r="F12" s="7">
-        <v>1279.7</v>
+      <c r="F12" s="8">
+        <v>2247.2979999999998</v>
       </c>
-      <c r="G12" s="7">
-        <v>740.95500000000004</v>
+      <c r="G12" s="8">
+        <v>1769.06</v>
       </c>
-      <c r="H12" s="7">
-        <v>914.93700000000001</v>
+      <c r="H12" s="8">
+        <v>2757.9479999999999</v>
       </c>
-      <c r="I12" s="7">
-        <v>1565.569</v>
+      <c r="I12" s="8">
+        <v>2833.9119999999998</v>
       </c>
-      <c r="J12" s="7">
-        <v>1223</v>
+      <c r="J12" s="8">
+        <v>2143.7710000000002</v>
       </c>
-      <c r="K12" s="7">
-        <v>720.66300000000001</v>
+      <c r="K12" s="8">
+        <v>1760.6659999999999</v>
       </c>
-      <c r="L12" s="7">
-        <v>909.86099999999999</v>
+      <c r="L12" s="8">
+        <v>2802.7060000000001</v>
       </c>
-      <c r="M12" s="7">
-        <v>1626.002</v>
+      <c r="M12" s="8">
+        <v>2875.8009999999999</v>
       </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8">
+        <v>9915.6779999999999</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>9504.6910000000007</v>
+      </c>
+      <c r="R12" s="8">
+        <v>9605.2070000000003</v>
+      </c>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
@@ -1889,45 +1949,171 @@
       <c r="CG12" s="7"/>
       <c r="CH12" s="7"/>
       <c r="CI12" s="7"/>
+      <c r="CJ12" s="3"/>
+      <c r="CK12" s="3"/>
+      <c r="CL12" s="3"/>
+      <c r="CM12" s="3"/>
+      <c r="CN12" s="3"/>
+      <c r="CO12" s="3"/>
+      <c r="CP12" s="3"/>
+      <c r="CQ12" s="3"/>
+      <c r="CR12" s="3"/>
+      <c r="CS12" s="3"/>
+      <c r="CT12" s="3"/>
+      <c r="CU12" s="3"/>
+      <c r="CV12" s="3"/>
+      <c r="CW12" s="3"/>
+      <c r="CX12" s="3"/>
+      <c r="CY12" s="3"/>
+      <c r="CZ12" s="3"/>
+      <c r="DA12" s="3"/>
+      <c r="DB12" s="3"/>
+      <c r="DC12" s="3"/>
+      <c r="DD12" s="3"/>
+      <c r="DE12" s="3"/>
+      <c r="DF12" s="3"/>
+      <c r="DG12" s="3"/>
+      <c r="DH12" s="3"/>
+      <c r="DI12" s="3"/>
+      <c r="DJ12" s="3"/>
+      <c r="DK12" s="3"/>
+      <c r="DL12" s="3"/>
+      <c r="DM12" s="3"/>
+      <c r="DN12" s="3"/>
+      <c r="DO12" s="3"/>
+      <c r="DP12" s="3"/>
+      <c r="DQ12" s="3"/>
+      <c r="DR12" s="3"/>
+      <c r="DS12" s="3"/>
+      <c r="DT12" s="3"/>
+      <c r="DU12" s="3"/>
+      <c r="DV12" s="3"/>
+      <c r="DW12" s="3"/>
+      <c r="DX12" s="3"/>
+      <c r="DY12" s="3"/>
+      <c r="DZ12" s="3"/>
+      <c r="EA12" s="3"/>
+      <c r="EB12" s="3"/>
+      <c r="EC12" s="3"/>
+      <c r="ED12" s="3"/>
+      <c r="EE12" s="3"/>
+      <c r="EF12" s="3"/>
+      <c r="EG12" s="3"/>
+      <c r="EH12" s="3"/>
+      <c r="EI12" s="3"/>
+      <c r="EJ12" s="3"/>
+      <c r="EK12" s="3"/>
+      <c r="EL12" s="3"/>
+      <c r="EM12" s="3"/>
+      <c r="EN12" s="3"/>
+      <c r="EO12" s="3"/>
+      <c r="EP12" s="3"/>
+      <c r="EQ12" s="3"/>
+      <c r="ER12" s="3"/>
+      <c r="ES12" s="3"/>
+      <c r="ET12" s="3"/>
+      <c r="EU12" s="3"/>
+      <c r="EV12" s="3"/>
+      <c r="EW12" s="3"/>
+      <c r="EX12" s="3"/>
+      <c r="EY12" s="3"/>
+      <c r="EZ12" s="3"/>
+      <c r="FA12" s="3"/>
+      <c r="FB12" s="3"/>
+      <c r="FC12" s="3"/>
+      <c r="FD12" s="3"/>
+      <c r="FE12" s="3"/>
+      <c r="FF12" s="3"/>
+      <c r="FG12" s="3"/>
+      <c r="FH12" s="3"/>
+      <c r="FI12" s="3"/>
+      <c r="FJ12" s="3"/>
+      <c r="FK12" s="3"/>
+      <c r="FL12" s="3"/>
+      <c r="FM12" s="3"/>
+      <c r="FN12" s="3"/>
+      <c r="FO12" s="3"/>
+      <c r="FP12" s="3"/>
+      <c r="FQ12" s="3"/>
+      <c r="FR12" s="3"/>
+      <c r="FS12" s="3"/>
+      <c r="FT12" s="3"/>
+      <c r="FU12" s="3"/>
+      <c r="FV12" s="3"/>
+      <c r="FW12" s="3"/>
+      <c r="FX12" s="3"/>
+      <c r="FY12" s="3"/>
+      <c r="FZ12" s="3"/>
+      <c r="GA12" s="3"/>
+      <c r="GB12" s="3"/>
+      <c r="GC12" s="3"/>
+      <c r="GD12" s="3"/>
+      <c r="GE12" s="3"/>
+      <c r="GF12" s="3"/>
+      <c r="GG12" s="3"/>
+      <c r="GH12" s="3"/>
+      <c r="GI12" s="3"/>
+      <c r="GJ12" s="3"/>
+      <c r="GK12" s="3"/>
+      <c r="GL12" s="3"/>
+      <c r="GM12" s="3"/>
+      <c r="GN12" s="3"/>
+      <c r="GO12" s="3"/>
+      <c r="GP12" s="3"/>
+      <c r="GQ12" s="3"/>
+      <c r="GR12" s="3"/>
+      <c r="GS12" s="3"/>
+      <c r="GT12" s="3"/>
+      <c r="GU12" s="3"/>
+      <c r="GV12" s="3"/>
+      <c r="GW12" s="3"/>
+      <c r="GX12" s="3"/>
+      <c r="GY12" s="3"/>
     </row>
     <row r="13" spans="1:207" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7">
-        <v>17.495000000000001</v>
+        <v>1261.1880000000001</v>
       </c>
       <c r="F13" s="7">
-        <v>0</v>
+        <v>1172.3620000000001</v>
       </c>
       <c r="G13" s="7">
-        <v>14.331</v>
+        <v>863.38199999999995</v>
       </c>
       <c r="H13" s="7">
-        <v>15.215</v>
+        <v>1317.3910000000001</v>
       </c>
       <c r="I13" s="7">
-        <v>17.405999999999999</v>
+        <v>1238.7380000000001</v>
       </c>
       <c r="J13" s="7">
-        <v>0</v>
+        <v>1001.3150000000001</v>
       </c>
       <c r="K13" s="7">
-        <v>15.497</v>
+        <v>811.66399999999999</v>
       </c>
       <c r="L13" s="7">
-        <v>15.898</v>
+        <v>1340.2619999999999</v>
       </c>
       <c r="M13" s="7">
-        <v>12.356</v>
+        <v>1247.46</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
+      <c r="P13" s="7">
+        <v>4803.3779999999997</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>4420.826</v>
+      </c>
+      <c r="R13" s="7">
+        <v>4343.4920000000002</v>
+      </c>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
@@ -1997,45 +2183,189 @@
       <c r="CG13" s="7"/>
       <c r="CH13" s="7"/>
       <c r="CI13" s="7"/>
+      <c r="CJ13" s="3"/>
+      <c r="CK13" s="3"/>
+      <c r="CL13" s="3"/>
+      <c r="CM13" s="3"/>
+      <c r="CN13" s="3"/>
+      <c r="CO13" s="3"/>
+      <c r="CP13" s="3"/>
+      <c r="CQ13" s="3"/>
+      <c r="CR13" s="3"/>
+      <c r="CS13" s="3"/>
+      <c r="CT13" s="3"/>
+      <c r="CU13" s="3"/>
+      <c r="CV13" s="3"/>
+      <c r="CW13" s="3"/>
+      <c r="CX13" s="3"/>
+      <c r="CY13" s="3"/>
+      <c r="CZ13" s="3"/>
+      <c r="DA13" s="3"/>
+      <c r="DB13" s="3"/>
+      <c r="DC13" s="3"/>
+      <c r="DD13" s="3"/>
+      <c r="DE13" s="3"/>
+      <c r="DF13" s="3"/>
+      <c r="DG13" s="3"/>
+      <c r="DH13" s="3"/>
+      <c r="DI13" s="3"/>
+      <c r="DJ13" s="3"/>
+      <c r="DK13" s="3"/>
+      <c r="DL13" s="3"/>
+      <c r="DM13" s="3"/>
+      <c r="DN13" s="3"/>
+      <c r="DO13" s="3"/>
+      <c r="DP13" s="3"/>
+      <c r="DQ13" s="3"/>
+      <c r="DR13" s="3"/>
+      <c r="DS13" s="3"/>
+      <c r="DT13" s="3"/>
+      <c r="DU13" s="3"/>
+      <c r="DV13" s="3"/>
+      <c r="DW13" s="3"/>
+      <c r="DX13" s="3"/>
+      <c r="DY13" s="3"/>
+      <c r="DZ13" s="3"/>
+      <c r="EA13" s="3"/>
+      <c r="EB13" s="3"/>
+      <c r="EC13" s="3"/>
+      <c r="ED13" s="3"/>
+      <c r="EE13" s="3"/>
+      <c r="EF13" s="3"/>
+      <c r="EG13" s="3"/>
+      <c r="EH13" s="3"/>
+      <c r="EI13" s="3"/>
+      <c r="EJ13" s="3"/>
+      <c r="EK13" s="3"/>
+      <c r="EL13" s="3"/>
+      <c r="EM13" s="3"/>
+      <c r="EN13" s="3"/>
+      <c r="EO13" s="3"/>
+      <c r="EP13" s="3"/>
+      <c r="EQ13" s="3"/>
+      <c r="ER13" s="3"/>
+      <c r="ES13" s="3"/>
+      <c r="ET13" s="3"/>
+      <c r="EU13" s="3"/>
+      <c r="EV13" s="3"/>
+      <c r="EW13" s="3"/>
+      <c r="EX13" s="3"/>
+      <c r="EY13" s="3"/>
+      <c r="EZ13" s="3"/>
+      <c r="FA13" s="3"/>
+      <c r="FB13" s="3"/>
+      <c r="FC13" s="3"/>
+      <c r="FD13" s="3"/>
+      <c r="FE13" s="3"/>
+      <c r="FF13" s="3"/>
+      <c r="FG13" s="3"/>
+      <c r="FH13" s="3"/>
+      <c r="FI13" s="3"/>
+      <c r="FJ13" s="3"/>
+      <c r="FK13" s="3"/>
+      <c r="FL13" s="3"/>
+      <c r="FM13" s="3"/>
+      <c r="FN13" s="3"/>
+      <c r="FO13" s="3"/>
+      <c r="FP13" s="3"/>
+      <c r="FQ13" s="3"/>
+      <c r="FR13" s="3"/>
+      <c r="FS13" s="3"/>
+      <c r="FT13" s="3"/>
+      <c r="FU13" s="3"/>
+      <c r="FV13" s="3"/>
+      <c r="FW13" s="3"/>
+      <c r="FX13" s="3"/>
+      <c r="FY13" s="3"/>
+      <c r="FZ13" s="3"/>
+      <c r="GA13" s="3"/>
+      <c r="GB13" s="3"/>
+      <c r="GC13" s="3"/>
+      <c r="GD13" s="3"/>
+      <c r="GE13" s="3"/>
+      <c r="GF13" s="3"/>
+      <c r="GG13" s="3"/>
+      <c r="GH13" s="3"/>
+      <c r="GI13" s="3"/>
+      <c r="GJ13" s="3"/>
+      <c r="GK13" s="3"/>
+      <c r="GL13" s="3"/>
+      <c r="GM13" s="3"/>
+      <c r="GN13" s="3"/>
+      <c r="GO13" s="3"/>
+      <c r="GP13" s="3"/>
+      <c r="GQ13" s="3"/>
+      <c r="GR13" s="3"/>
+      <c r="GS13" s="3"/>
+      <c r="GT13" s="3"/>
+      <c r="GU13" s="3"/>
+      <c r="GV13" s="3"/>
+      <c r="GW13" s="3"/>
+      <c r="GX13" s="3"/>
+      <c r="GY13" s="3"/>
     </row>
     <row r="14" spans="1:207" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
-        <v>19</v>
+      <c r="B14" s="2" t="s">
+        <v>21</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8">
-        <v>2780.194</v>
+      <c r="C14" s="7">
+        <f t="shared" ref="C14:H14" si="0">+C12-C13</f>
+        <v>0</v>
       </c>
-      <c r="F14" s="8">
-        <v>2247.2979999999998</v>
+      <c r="D14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
-      <c r="G14" s="8">
-        <v>1769.06</v>
+      <c r="E14" s="7">
+        <f t="shared" si="0"/>
+        <v>1519.0059999999999</v>
       </c>
-      <c r="H14" s="8">
-        <v>2757.9479999999999</v>
+      <c r="F14" s="7">
+        <f t="shared" si="0"/>
+        <v>1074.9359999999997</v>
       </c>
-      <c r="I14" s="8">
-        <v>2833.9119999999998</v>
+      <c r="G14" s="7">
+        <f t="shared" si="0"/>
+        <v>905.678</v>
       </c>
-      <c r="J14" s="8">
-        <v>2143.7710000000002</v>
+      <c r="H14" s="7">
+        <f t="shared" si="0"/>
+        <v>1440.5569999999998</v>
       </c>
-      <c r="K14" s="8">
-        <v>1760.6659999999999</v>
+      <c r="I14" s="7">
+        <f>+I12-I13</f>
+        <v>1595.1739999999998</v>
       </c>
-      <c r="L14" s="8">
-        <v>2802.7060000000001</v>
+      <c r="J14" s="7">
+        <f t="shared" ref="J14:M14" si="1">+J12-J13</f>
+        <v>1142.4560000000001</v>
       </c>
-      <c r="M14" s="8">
-        <v>2875.8009999999999</v>
+      <c r="K14" s="7">
+        <f t="shared" si="1"/>
+        <v>949.00199999999995</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="1"/>
+        <v>1462.4440000000002</v>
+      </c>
+      <c r="M14" s="7">
+        <f t="shared" si="1"/>
+        <v>1628.3409999999999</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
+      <c r="P14" s="7">
+        <f>+P12-P13</f>
+        <v>5112.3</v>
+      </c>
+      <c r="Q14" s="7">
+        <f>+Q12-Q13</f>
+        <v>5083.8650000000007</v>
+      </c>
+      <c r="R14" s="7">
+        <f>+R12-R13</f>
+        <v>5261.7150000000001</v>
+      </c>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
@@ -2228,42 +2558,48 @@
     </row>
     <row r="15" spans="1:207" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7">
-        <v>1261.1880000000001</v>
+        <v>1353.152</v>
       </c>
       <c r="F15" s="7">
-        <v>1172.3620000000001</v>
+        <v>1197.8489999999999</v>
       </c>
       <c r="G15" s="7">
-        <v>863.38199999999995</v>
+        <v>1028.6980000000001</v>
       </c>
       <c r="H15" s="7">
-        <v>1317.3910000000001</v>
+        <v>1166.654</v>
       </c>
       <c r="I15" s="7">
-        <v>1238.7380000000001</v>
+        <v>1318.3969999999999</v>
       </c>
       <c r="J15" s="7">
-        <v>1001.3150000000001</v>
+        <v>1177.1010000000001</v>
       </c>
       <c r="K15" s="7">
-        <v>811.66399999999999</v>
+        <v>1035.6110000000001</v>
       </c>
       <c r="L15" s="7">
-        <v>1340.2619999999999</v>
+        <v>1149.8240000000001</v>
       </c>
       <c r="M15" s="7">
-        <v>1247.46</v>
+        <v>1308.5709999999999</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
+      <c r="P15" s="7">
+        <v>4748.6689999999999</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>4690.8500000000004</v>
+      </c>
+      <c r="R15" s="7">
+        <v>4654.43</v>
+      </c>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
@@ -2456,57 +2792,48 @@
     </row>
     <row r="16" spans="1:207" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
-      <c r="C16" s="7">
-        <f t="shared" ref="C16:H16" si="0">+C14-C15</f>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7">
+        <v>257.096</v>
+      </c>
+      <c r="F16" s="7">
+        <v>250.47</v>
+      </c>
+      <c r="G16" s="7">
         <v>0</v>
       </c>
-      <c r="D16" s="7">
-        <f t="shared" si="0"/>
+      <c r="H16" s="7">
         <v>0</v>
       </c>
-      <c r="E16" s="7">
-        <f t="shared" si="0"/>
-        <v>1519.0059999999999</v>
-      </c>
-      <c r="F16" s="7">
-        <f t="shared" si="0"/>
-        <v>1074.9359999999997</v>
-      </c>
-      <c r="G16" s="7">
-        <f t="shared" si="0"/>
-        <v>905.678</v>
-      </c>
-      <c r="H16" s="7">
-        <f t="shared" si="0"/>
-        <v>1440.5569999999998</v>
-      </c>
       <c r="I16" s="7">
-        <f>+I14-I15</f>
-        <v>1595.1739999999998</v>
+        <v>51</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" ref="J16:M16" si="1">+J14-J15</f>
-        <v>1142.4560000000001</v>
+        <v>38.241999999999997</v>
       </c>
       <c r="K16" s="7">
-        <f t="shared" si="1"/>
-        <v>949.00199999999995</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7">
-        <f t="shared" si="1"/>
-        <v>1462.4440000000002</v>
+        <v>0</v>
       </c>
       <c r="M16" s="7">
-        <f t="shared" si="1"/>
-        <v>1628.3409999999999</v>
+        <v>30.716000000000001</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
+      <c r="P16" s="7">
+        <v>507.56599999999997</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>89.242000000000004</v>
+      </c>
+      <c r="R16" s="7">
+        <v>30.716000000000001</v>
+      </c>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
@@ -2699,42 +3026,66 @@
     </row>
     <row r="17" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="C17" s="7">
+        <f t="shared" ref="C17" si="2">+C14-C15-C16</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" ref="D17" si="3">+D14-D15-D16</f>
+        <v>0</v>
+      </c>
       <c r="E17" s="7">
-        <v>1353.152</v>
+        <f t="shared" ref="E17:H17" si="4">+E14-E15-E16</f>
+        <v>-91.242000000000189</v>
       </c>
       <c r="F17" s="7">
-        <v>1197.8489999999999</v>
+        <f t="shared" si="4"/>
+        <v>-373.38300000000027</v>
       </c>
       <c r="G17" s="7">
-        <v>1028.6980000000001</v>
+        <f t="shared" si="4"/>
+        <v>-123.0200000000001</v>
       </c>
       <c r="H17" s="7">
-        <v>1166.654</v>
+        <f t="shared" si="4"/>
+        <v>273.90299999999979</v>
       </c>
       <c r="I17" s="7">
-        <v>1318.3969999999999</v>
+        <f>+I14-I15-I16</f>
+        <v>225.77699999999982</v>
       </c>
       <c r="J17" s="7">
-        <v>1177.1010000000001</v>
+        <f t="shared" ref="J17:M17" si="5">+J14-J15-J16</f>
+        <v>-72.886999999999972</v>
       </c>
       <c r="K17" s="7">
-        <v>1035.6110000000001</v>
+        <f t="shared" si="5"/>
+        <v>-86.609000000000151</v>
       </c>
       <c r="L17" s="7">
-        <v>1149.8240000000001</v>
+        <f t="shared" si="5"/>
+        <v>312.62000000000012</v>
       </c>
       <c r="M17" s="7">
-        <v>1308.5709999999999</v>
+        <f t="shared" si="5"/>
+        <v>289.05399999999997</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
+      <c r="P17" s="7">
+        <f t="shared" ref="P17:R17" si="6">+P14-P15-P16</f>
+        <v>-143.93499999999966</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="6"/>
+        <v>303.77300000000031</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="6"/>
+        <v>576.56899999999985</v>
+      </c>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
@@ -2927,42 +3278,48 @@
     </row>
     <row r="18" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <v>257.096</v>
+        <v>3.5649999999999999</v>
       </c>
       <c r="F18" s="7">
-        <v>250.47</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7">
+        <v>3.395</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3.6779999999999999</v>
+      </c>
+      <c r="I18" s="7">
+        <v>6.8259999999999996</v>
+      </c>
+      <c r="J18" s="7">
         <v>0</v>
       </c>
-      <c r="H18" s="7">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7">
-        <v>51</v>
-      </c>
-      <c r="J18" s="7">
-        <v>38.241999999999997</v>
-      </c>
       <c r="K18" s="7">
-        <v>0</v>
+        <v>2.5179999999999998</v>
       </c>
       <c r="L18" s="7">
-        <v>0</v>
+        <v>3.4079999999999999</v>
       </c>
       <c r="M18" s="7">
-        <v>30.716000000000001</v>
+        <v>5.1360000000000001</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
+      <c r="P18" s="7">
+        <v>20.245999999999999</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>24.783000000000001</v>
+      </c>
+      <c r="R18" s="7">
+        <v>18.027999999999999</v>
+      </c>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
@@ -3155,57 +3512,48 @@
     </row>
     <row r="19" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
-      <c r="C19" s="7">
-        <f t="shared" ref="C19" si="2">+C16-C17-C18</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="7">
-        <f t="shared" ref="D19" si="3">+D16-D17-D18</f>
-        <v>0</v>
-      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="7">
-        <f t="shared" ref="E19:H19" si="4">+E16-E17-E18</f>
-        <v>-91.242000000000189</v>
+        <v>52.661000000000001</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="4"/>
-        <v>-373.38300000000027</v>
+        <v>39.896000000000001</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="4"/>
-        <v>-123.0200000000001</v>
+        <v>44.341999999999999</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="4"/>
-        <v>273.90299999999979</v>
+        <v>46.366</v>
       </c>
       <c r="I19" s="7">
-        <f>+I16-I17-I18</f>
-        <v>225.77699999999982</v>
+        <v>43.341999999999999</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" ref="J19:M19" si="5">+J16-J17-J18</f>
-        <v>-72.886999999999972</v>
+        <v>29.091999999999999</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" si="5"/>
-        <v>-86.609000000000151</v>
+        <v>43.637999999999998</v>
       </c>
       <c r="L19" s="7">
-        <f t="shared" si="5"/>
-        <v>312.62000000000012</v>
+        <v>49.616999999999997</v>
       </c>
       <c r="M19" s="7">
-        <f t="shared" si="5"/>
-        <v>289.05399999999997</v>
+        <v>39.747</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
+      <c r="P19" s="7">
+        <v>185.92500000000001</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>174.136</v>
+      </c>
+      <c r="R19" s="7">
+        <v>166.77099999999999</v>
+      </c>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
@@ -3398,42 +3746,48 @@
     </row>
     <row r="20" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7">
-        <v>3.5649999999999999</v>
+        <v>29.004000000000001</v>
       </c>
       <c r="F20" s="7">
-        <v>0</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="G20" s="7">
-        <v>3.395</v>
+        <v>-1.486</v>
       </c>
       <c r="H20" s="7">
-        <v>3.6779999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="I20" s="7">
-        <v>6.8259999999999996</v>
+        <v>7.4080000000000004</v>
       </c>
       <c r="J20" s="7">
-        <v>0</v>
+        <v>-14.631</v>
       </c>
       <c r="K20" s="7">
-        <v>2.5179999999999998</v>
+        <v>1.1359999999999999</v>
       </c>
       <c r="L20" s="7">
-        <v>3.4079999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="M20" s="7">
-        <v>5.1360000000000001</v>
+        <v>108.416</v>
       </c>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
+      <c r="P20" s="7">
+        <v>24.693000000000001</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>-9.3689999999999998</v>
+      </c>
+      <c r="R20" s="7">
+        <v>-86.608000000000004</v>
+      </c>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
@@ -3626,42 +3980,66 @@
     </row>
     <row r="21" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="C21" s="7">
+        <f t="shared" ref="C21:H21" si="7">+C17+C18-C19+C20</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="E21" s="7">
-        <v>52.661000000000001</v>
+        <f t="shared" si="7"/>
+        <v>-111.33400000000019</v>
       </c>
       <c r="F21" s="7">
-        <v>39.896000000000001</v>
+        <f t="shared" si="7"/>
+        <v>-411.76400000000029</v>
       </c>
       <c r="G21" s="7">
-        <v>44.341999999999999</v>
+        <f t="shared" si="7"/>
+        <v>-165.45300000000009</v>
       </c>
       <c r="H21" s="7">
-        <v>46.366</v>
+        <f t="shared" si="7"/>
+        <v>230.55499999999981</v>
       </c>
       <c r="I21" s="7">
-        <v>43.341999999999999</v>
+        <f>+I17+I18-I19+I20</f>
+        <v>196.66899999999978</v>
       </c>
       <c r="J21" s="7">
-        <v>29.091999999999999</v>
+        <f t="shared" ref="J21:M21" si="8">+J17+J18-J19+J20</f>
+        <v>-116.60999999999997</v>
       </c>
       <c r="K21" s="7">
-        <v>43.637999999999998</v>
+        <f t="shared" si="8"/>
+        <v>-126.59300000000016</v>
       </c>
       <c r="L21" s="7">
-        <v>49.616999999999997</v>
+        <f t="shared" si="8"/>
+        <v>268.28100000000012</v>
       </c>
       <c r="M21" s="7">
-        <v>39.747</v>
+        <f t="shared" si="8"/>
+        <v>362.85899999999998</v>
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
+      <c r="P21" s="7">
+        <f t="shared" ref="P21:R21" si="9">+P17+P18-P19+P20</f>
+        <v>-284.92099999999971</v>
+      </c>
+      <c r="Q21" s="7">
+        <f t="shared" si="9"/>
+        <v>145.05100000000033</v>
+      </c>
+      <c r="R21" s="7">
+        <f t="shared" si="9"/>
+        <v>341.2179999999999</v>
+      </c>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
@@ -3854,42 +4232,48 @@
     </row>
     <row r="22" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7">
-        <v>29.004000000000001</v>
+        <v>-19.597999999999999</v>
       </c>
       <c r="F22" s="7">
-        <v>1.5149999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="G22" s="7">
-        <v>-1.486</v>
+        <v>-13.426</v>
       </c>
       <c r="H22" s="7">
-        <v>-0.66</v>
+        <v>28.045999999999999</v>
       </c>
       <c r="I22" s="7">
-        <v>7.4080000000000004</v>
+        <v>27.56</v>
       </c>
       <c r="J22" s="7">
-        <v>-14.631</v>
+        <v>33.656999999999996</v>
       </c>
       <c r="K22" s="7">
-        <v>1.1359999999999999</v>
+        <v>-10.185</v>
       </c>
       <c r="L22" s="7">
-        <v>1.87</v>
+        <v>78.516000000000005</v>
       </c>
       <c r="M22" s="7">
-        <v>108.416</v>
+        <v>62.014000000000003</v>
       </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
+      <c r="P22" s="7">
+        <v>733.55600000000004</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>75.837000000000003</v>
+      </c>
+      <c r="R22" s="7">
+        <v>86.298000000000002</v>
+      </c>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
@@ -4082,57 +4466,66 @@
     </row>
     <row r="23" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C23" s="7">
-        <f t="shared" ref="C23:H23" si="6">+C19+C20-C21+C22</f>
+        <f t="shared" ref="C23:H23" si="10">+C21-C22</f>
         <v>0</v>
       </c>
       <c r="D23" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E23" s="7">
-        <f t="shared" si="6"/>
-        <v>-111.33400000000019</v>
+        <f t="shared" si="10"/>
+        <v>-91.736000000000189</v>
       </c>
       <c r="F23" s="7">
-        <f t="shared" si="6"/>
-        <v>-411.76400000000029</v>
+        <f t="shared" si="10"/>
+        <v>-412.12400000000031</v>
       </c>
       <c r="G23" s="7">
-        <f t="shared" si="6"/>
-        <v>-165.45300000000009</v>
+        <f t="shared" si="10"/>
+        <v>-152.0270000000001</v>
       </c>
       <c r="H23" s="7">
-        <f t="shared" si="6"/>
-        <v>230.55499999999981</v>
+        <f t="shared" si="10"/>
+        <v>202.50899999999982</v>
       </c>
       <c r="I23" s="7">
-        <f>+I19+I20-I21+I22</f>
-        <v>196.66899999999978</v>
+        <f>+I21-I22</f>
+        <v>169.10899999999978</v>
       </c>
       <c r="J23" s="7">
-        <f t="shared" ref="J23:M23" si="7">+J19+J20-J21+J22</f>
-        <v>-116.60999999999997</v>
+        <f t="shared" ref="J23:M23" si="11">+J21-J22</f>
+        <v>-150.26699999999997</v>
       </c>
       <c r="K23" s="7">
-        <f t="shared" si="7"/>
-        <v>-126.59300000000016</v>
+        <f t="shared" si="11"/>
+        <v>-116.40800000000016</v>
       </c>
       <c r="L23" s="7">
-        <f t="shared" si="7"/>
-        <v>268.28100000000012</v>
+        <f t="shared" si="11"/>
+        <v>189.7650000000001</v>
       </c>
       <c r="M23" s="7">
-        <f t="shared" si="7"/>
-        <v>362.85899999999998</v>
+        <f t="shared" si="11"/>
+        <v>300.84499999999997</v>
       </c>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
+      <c r="P23" s="7">
+        <f t="shared" ref="P23:R23" si="12">+P21-P22</f>
+        <v>-1018.4769999999997</v>
+      </c>
+      <c r="Q23" s="7">
+        <f t="shared" si="12"/>
+        <v>69.214000000000325</v>
+      </c>
+      <c r="R23" s="7">
+        <f t="shared" si="12"/>
+        <v>254.9199999999999</v>
+      </c>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
@@ -4325,42 +4718,48 @@
     </row>
     <row r="24" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7">
-        <v>-19.597999999999999</v>
+        <v>-49.283999999999999</v>
       </c>
       <c r="F24" s="7">
-        <v>0.36</v>
+        <v>6.1840000000000002</v>
       </c>
       <c r="G24" s="7">
-        <v>-13.426</v>
+        <v>106.85899999999999</v>
       </c>
       <c r="H24" s="7">
-        <v>28.045999999999999</v>
+        <v>150.33099999999999</v>
       </c>
       <c r="I24" s="7">
-        <v>27.56</v>
+        <v>1.329</v>
       </c>
       <c r="J24" s="7">
-        <v>33.656999999999996</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="K24" s="7">
-        <v>-10.185</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7">
-        <v>78.516000000000005</v>
+        <v>0</v>
       </c>
       <c r="M24" s="7">
-        <v>62.014000000000003</v>
+        <v>0</v>
       </c>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
+      <c r="P24" s="7">
+        <v>-49.594999999999999</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>259.04000000000002</v>
+      </c>
+      <c r="R24" s="7">
+        <v>0</v>
+      </c>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
@@ -4553,57 +4952,66 @@
     </row>
     <row r="25" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C25" s="7">
-        <f t="shared" ref="C25:H25" si="8">+C23-C24</f>
+        <f t="shared" ref="C25:H25" si="13">+C23-C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E25" s="7">
-        <f t="shared" si="8"/>
-        <v>-91.736000000000189</v>
+        <f t="shared" si="13"/>
+        <v>-42.45200000000019</v>
       </c>
       <c r="F25" s="7">
-        <f t="shared" si="8"/>
-        <v>-412.12400000000031</v>
+        <f t="shared" si="13"/>
+        <v>-418.30800000000033</v>
       </c>
       <c r="G25" s="7">
-        <f t="shared" si="8"/>
-        <v>-152.0270000000001</v>
+        <f t="shared" si="13"/>
+        <v>-258.88600000000008</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="8"/>
-        <v>202.50899999999982</v>
+        <f t="shared" si="13"/>
+        <v>52.177999999999827</v>
       </c>
       <c r="I25" s="7">
         <f>+I23-I24</f>
-        <v>169.10899999999978</v>
+        <v>167.77999999999977</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" ref="J25:M25" si="9">+J23-J24</f>
-        <v>-150.26699999999997</v>
+        <f t="shared" ref="J25:M25" si="14">+J23-J24</f>
+        <v>-150.78799999999995</v>
       </c>
       <c r="K25" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>-116.40800000000016</v>
       </c>
       <c r="L25" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>189.7650000000001</v>
       </c>
       <c r="M25" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>300.84499999999997</v>
       </c>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
+      <c r="P25" s="7">
+        <f t="shared" ref="P25:Q25" si="15">+P23-P24</f>
+        <v>-968.88199999999972</v>
+      </c>
+      <c r="Q25" s="7">
+        <f t="shared" si="15"/>
+        <v>-189.82599999999968</v>
+      </c>
+      <c r="R25" s="7">
+        <f>+R23-R24</f>
+        <v>254.9199999999999</v>
+      </c>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
@@ -4795,38 +5203,17 @@
       <c r="GY25" s="3"/>
     </row>
     <row r="26" spans="2:207" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="7">
-        <v>-49.283999999999999</v>
-      </c>
-      <c r="F26" s="7">
-        <v>6.1840000000000002</v>
-      </c>
-      <c r="G26" s="7">
-        <v>106.85899999999999</v>
-      </c>
-      <c r="H26" s="7">
-        <v>150.33099999999999</v>
-      </c>
-      <c r="I26" s="7">
-        <v>1.329</v>
-      </c>
-      <c r="J26" s="7">
-        <v>0.52100000000000002</v>
-      </c>
-      <c r="K26" s="7">
-        <v>0</v>
-      </c>
-      <c r="L26" s="7">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7">
-        <v>0</v>
-      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
@@ -5024,57 +5411,66 @@
     </row>
     <row r="27" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
-      <c r="C27" s="7">
-        <f t="shared" ref="C27:H27" si="10">+C25-C26</f>
-        <v>0</v>
+      <c r="C27" s="9" t="e">
+        <f t="shared" ref="C27:D27" si="16">+C25/C28</f>
+        <v>#DIV/0!</v>
       </c>
-      <c r="D27" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
+      <c r="D27" s="9" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
       </c>
-      <c r="E27" s="7">
-        <f t="shared" si="10"/>
-        <v>-42.45200000000019</v>
+      <c r="E27" s="9">
+        <f>+E25/E28</f>
+        <v>-0.10930447522162451</v>
       </c>
-      <c r="F27" s="7">
-        <f t="shared" si="10"/>
-        <v>-418.30800000000033</v>
+      <c r="F27" s="9">
+        <f t="shared" ref="F27:M27" si="17">+F25/F28</f>
+        <v>-1.0765623753406826</v>
       </c>
-      <c r="G27" s="7">
-        <f t="shared" si="10"/>
-        <v>-258.88600000000008</v>
+      <c r="G27" s="9">
+        <f t="shared" si="17"/>
+        <v>-0.66596011225983387</v>
       </c>
-      <c r="H27" s="7">
-        <f t="shared" si="10"/>
-        <v>52.177999999999827</v>
+      <c r="H27" s="9">
+        <f t="shared" si="17"/>
+        <v>0.13411850587594162</v>
       </c>
-      <c r="I27" s="7">
-        <f>+I25-I26</f>
-        <v>167.77999999999977</v>
+      <c r="I27" s="9">
+        <f t="shared" si="17"/>
+        <v>0.43106947777338089</v>
       </c>
-      <c r="J27" s="7">
-        <f t="shared" ref="J27:M27" si="11">+J25-J26</f>
-        <v>-150.78799999999995</v>
+      <c r="J27" s="9">
+        <f t="shared" si="17"/>
+        <v>-0.38702788721910641</v>
       </c>
-      <c r="K27" s="7">
-        <f t="shared" si="11"/>
-        <v>-116.40800000000016</v>
+      <c r="K27" s="9">
+        <f t="shared" si="17"/>
+        <v>-0.2984636842860956</v>
       </c>
-      <c r="L27" s="7">
-        <f t="shared" si="11"/>
-        <v>189.7650000000001</v>
+      <c r="L27" s="9">
+        <f t="shared" si="17"/>
+        <v>0.48576979787430141</v>
       </c>
-      <c r="M27" s="7">
-        <f t="shared" si="11"/>
-        <v>300.84499999999997</v>
+      <c r="M27" s="9">
+        <f t="shared" si="17"/>
+        <v>0.7695918550068428</v>
       </c>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
+      <c r="P27" s="9">
+        <f t="shared" ref="P27:Q27" si="18">+P25/P28</f>
+        <v>-2.4971185567010301</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" si="18"/>
+        <v>-0.48779397253515255</v>
+      </c>
+      <c r="R27" s="9">
+        <f>+R25/R28</f>
+        <v>0.65240480218253083</v>
+      </c>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
@@ -5266,22 +5662,49 @@
       <c r="GY27" s="3"/>
     </row>
     <row r="28" spans="2:207" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
+      <c r="E28" s="7">
+        <v>388.38299999999998</v>
+      </c>
+      <c r="F28" s="7">
+        <v>388.55900000000003</v>
+      </c>
+      <c r="G28" s="7">
+        <v>388.74099999999999</v>
+      </c>
+      <c r="H28" s="7">
+        <v>389.04399999999998</v>
+      </c>
+      <c r="I28" s="7">
+        <v>389.21800000000002</v>
+      </c>
+      <c r="J28" s="7">
+        <v>389.60500000000002</v>
+      </c>
+      <c r="K28" s="7">
+        <v>390.024</v>
+      </c>
+      <c r="L28" s="7">
+        <v>390.64800000000002</v>
+      </c>
+      <c r="M28" s="7">
+        <v>390.91500000000002</v>
+      </c>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
+      <c r="P28" s="7">
+        <v>388</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>389.15199999999999</v>
+      </c>
+      <c r="R28" s="7">
+        <v>390.73899999999998</v>
+      </c>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -5473,53 +5896,17 @@
       <c r="GY28" s="3"/>
     </row>
     <row r="29" spans="2:207" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="9" t="e">
-        <f t="shared" ref="C29:D29" si="12">+C27/C30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D29" s="9" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E29" s="9">
-        <f>+E27/E30</f>
-        <v>-0.10930447522162451</v>
-      </c>
-      <c r="F29" s="9">
-        <f t="shared" ref="F29:M29" si="13">+F27/F30</f>
-        <v>-1.0765623753406826</v>
-      </c>
-      <c r="G29" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.66596011225983387</v>
-      </c>
-      <c r="H29" s="9">
-        <f t="shared" si="13"/>
-        <v>0.13411850587594162</v>
-      </c>
-      <c r="I29" s="9">
-        <f t="shared" si="13"/>
-        <v>0.43106947777338089</v>
-      </c>
-      <c r="J29" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.38702788721910641</v>
-      </c>
-      <c r="K29" s="9">
-        <f t="shared" si="13"/>
-        <v>-0.2984636842860956</v>
-      </c>
-      <c r="L29" s="9">
-        <f t="shared" si="13"/>
-        <v>0.48576979787430141</v>
-      </c>
-      <c r="M29" s="9">
-        <f t="shared" si="13"/>
-        <v>0.7695918550068428</v>
-      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
@@ -5716,45 +6103,48 @@
       <c r="GY29" s="3"/>
     </row>
     <row r="30" spans="2:207" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>5</v>
+      <c r="B30" s="1" t="s">
+        <v>48</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7">
-        <v>388.38299999999998</v>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="12" t="e">
+        <f t="shared" ref="G30:K30" si="19">+G12/C12-1</f>
+        <v>#DIV/0!</v>
       </c>
-      <c r="F30" s="7">
-        <v>388.55900000000003</v>
+      <c r="H30" s="12" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
       </c>
-      <c r="G30" s="7">
-        <v>388.74099999999999</v>
+      <c r="I30" s="12">
+        <f t="shared" si="19"/>
+        <v>1.9321673235752623E-2</v>
       </c>
-      <c r="H30" s="7">
-        <v>389.04399999999998</v>
+      <c r="J30" s="12">
+        <f t="shared" si="19"/>
+        <v>-4.6067321734811983E-2</v>
       </c>
-      <c r="I30" s="7">
-        <v>389.21800000000002</v>
+      <c r="K30" s="12">
+        <f t="shared" si="19"/>
+        <v>-4.74489276791068E-3</v>
       </c>
-      <c r="J30" s="7">
-        <v>389.60500000000002</v>
+      <c r="L30" s="12">
+        <f>+L12/H12-1</f>
+        <v>1.6228732376390109E-2</v>
       </c>
-      <c r="K30" s="7">
-        <v>390.024</v>
+      <c r="M30" s="12">
+        <f>+M12/I12-1</f>
+        <v>1.4781334071064967E-2</v>
       </c>
-      <c r="L30" s="7">
-        <v>390.64800000000002</v>
-      </c>
-      <c r="M30" s="7">
-        <v>390.91500000000002</v>
-      </c>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
       <c r="U30" s="7"/>
       <c r="V30" s="7"/>
       <c r="W30" s="7"/>
@@ -5944,17 +6334,53 @@
       <c r="GY30" s="3"/>
     </row>
     <row r="31" spans="2:207" x14ac:dyDescent="0.2">
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
+      <c r="B31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="13" t="e">
+        <f t="shared" ref="C31" si="20">+C14/C12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D31" s="13" t="e">
+        <f t="shared" ref="D31:K31" si="21">+D14/D12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.54636690820856382</v>
+      </c>
+      <c r="F31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.47832374700640495</v>
+      </c>
+      <c r="G31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.51195437124800747</v>
+      </c>
+      <c r="H31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.52232928249553645</v>
+      </c>
+      <c r="I31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.56288762671529669</v>
+      </c>
+      <c r="J31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.53291886120299237</v>
+      </c>
+      <c r="K31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.53900171866782232</v>
+      </c>
+      <c r="L31" s="13">
+        <f>+L14/L12</f>
+        <v>0.52179714889824336</v>
+      </c>
+      <c r="M31" s="13">
+        <f>+M14/M12</f>
+        <v>0.56622172396490578</v>
+      </c>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
@@ -6151,48 +6577,60 @@
       <c r="GY31" s="3"/>
     </row>
     <row r="32" spans="2:207" x14ac:dyDescent="0.2">
-      <c r="B32" s="1" t="s">
-        <v>54</v>
+      <c r="B32" s="11" t="s">
+        <v>50</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="12" t="e">
-        <f t="shared" ref="G32:K32" si="14">+G14/C14-1</f>
+      <c r="C32" s="13" t="e">
+        <f t="shared" ref="C32" si="22">+C17/C12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="12" t="e">
-        <f t="shared" si="14"/>
+      <c r="D32" s="13" t="e">
+        <f t="shared" ref="D32:K32" si="23">+D17/D12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I32" s="12">
-        <f t="shared" si="14"/>
-        <v>1.9321673235752623E-2</v>
+      <c r="E32" s="13">
+        <f t="shared" si="23"/>
+        <v>-3.2818573092381391E-2</v>
       </c>
-      <c r="J32" s="12">
-        <f t="shared" si="14"/>
-        <v>-4.6067321734811983E-2</v>
+      <c r="F32" s="13">
+        <f t="shared" si="23"/>
+        <v>-0.16614752471634839</v>
       </c>
-      <c r="K32" s="12">
-        <f t="shared" si="14"/>
-        <v>-4.74489276791068E-3</v>
+      <c r="G32" s="13">
+        <f t="shared" si="23"/>
+        <v>-6.9539755576407861E-2</v>
       </c>
-      <c r="L32" s="12">
-        <f>+L14/H14-1</f>
-        <v>1.6228732376390109E-2</v>
+      <c r="H32" s="13">
+        <f t="shared" si="23"/>
+        <v>9.9314055232368345E-2</v>
       </c>
-      <c r="M32" s="12">
-        <f>+M14/I14-1</f>
-        <v>1.4781334071064967E-2</v>
+      <c r="I32" s="13">
+        <f t="shared" si="23"/>
+        <v>7.9669728629541012E-2</v>
       </c>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="8"/>
+      <c r="J32" s="13">
+        <f t="shared" si="23"/>
+        <v>-3.3999433708171239E-2</v>
+      </c>
+      <c r="K32" s="13">
+        <f t="shared" si="23"/>
+        <v>-4.9191044752383561E-2</v>
+      </c>
+      <c r="L32" s="13">
+        <f>+L17/L12</f>
+        <v>0.11154220242865291</v>
+      </c>
+      <c r="M32" s="13">
+        <f>+M17/M12</f>
+        <v>0.10051251807757212</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
       <c r="W32" s="7"/>
@@ -6383,51 +6821,51 @@
     </row>
     <row r="33" spans="2:207" x14ac:dyDescent="0.2">
       <c r="B33" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C33" s="13" t="e">
-        <f t="shared" ref="C33" si="15">+C16/C14</f>
+        <f t="shared" ref="C33" si="24">+C22/C21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="13" t="e">
-        <f t="shared" ref="D33:K33" si="16">+D16/D14</f>
+        <f t="shared" ref="D33:K33" si="25">+D22/D21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="13">
-        <f t="shared" si="16"/>
-        <v>0.54636690820856382</v>
+        <f t="shared" si="25"/>
+        <v>0.17602888605457423</v>
       </c>
       <c r="F33" s="13">
-        <f t="shared" si="16"/>
-        <v>0.47832374700640495</v>
+        <f t="shared" si="25"/>
+        <v>-8.7428721306379313E-4</v>
       </c>
       <c r="G33" s="13">
-        <f t="shared" si="16"/>
-        <v>0.51195437124800747</v>
+        <f t="shared" si="25"/>
+        <v>8.1146911811813591E-2</v>
       </c>
       <c r="H33" s="13">
-        <f t="shared" si="16"/>
-        <v>0.52232928249553645</v>
+        <f t="shared" si="25"/>
+        <v>0.12164559432673341</v>
       </c>
       <c r="I33" s="13">
-        <f t="shared" si="16"/>
-        <v>0.56288762671529669</v>
+        <f t="shared" si="25"/>
+        <v>0.1401339306143827</v>
       </c>
       <c r="J33" s="13">
-        <f t="shared" si="16"/>
-        <v>0.53291886120299237</v>
+        <f t="shared" si="25"/>
+        <v>-0.28862876254180608</v>
       </c>
       <c r="K33" s="13">
-        <f t="shared" si="16"/>
-        <v>0.53900171866782232</v>
+        <f t="shared" si="25"/>
+        <v>8.0454685488139055E-2</v>
       </c>
       <c r="L33" s="13">
-        <f>+L16/L14</f>
-        <v>0.52179714889824336</v>
+        <f>+L22/L21</f>
+        <v>0.29266328961052018</v>
       </c>
       <c r="M33" s="13">
-        <f>+M16/M14</f>
-        <v>0.56622172396490578</v>
+        <f>+M22/M21</f>
+        <v>0.17090384970470626</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
@@ -6625,53 +7063,17 @@
       <c r="GY33" s="3"/>
     </row>
     <row r="34" spans="2:207" x14ac:dyDescent="0.2">
-      <c r="B34" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="13" t="e">
-        <f t="shared" ref="C34" si="17">+C19/C14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D34" s="13" t="e">
-        <f t="shared" ref="D34:K34" si="18">+D19/D14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E34" s="13">
-        <f t="shared" si="18"/>
-        <v>-3.2818573092381391E-2</v>
-      </c>
-      <c r="F34" s="13">
-        <f t="shared" si="18"/>
-        <v>-0.16614752471634839</v>
-      </c>
-      <c r="G34" s="13">
-        <f t="shared" si="18"/>
-        <v>-6.9539755576407861E-2</v>
-      </c>
-      <c r="H34" s="13">
-        <f t="shared" si="18"/>
-        <v>9.9314055232368345E-2</v>
-      </c>
-      <c r="I34" s="13">
-        <f t="shared" si="18"/>
-        <v>7.9669728629541012E-2</v>
-      </c>
-      <c r="J34" s="13">
-        <f t="shared" si="18"/>
-        <v>-3.3999433708171239E-2</v>
-      </c>
-      <c r="K34" s="13">
-        <f t="shared" si="18"/>
-        <v>-4.9191044752383561E-2</v>
-      </c>
-      <c r="L34" s="13">
-        <f>+L19/L14</f>
-        <v>0.11154220242865291</v>
-      </c>
-      <c r="M34" s="13">
-        <f>+M19/M14</f>
-        <v>0.10051251807757212</v>
-      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
       <c r="N34" s="7"/>
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
@@ -6868,53 +7270,17 @@
       <c r="GY34" s="3"/>
     </row>
     <row r="35" spans="2:207" x14ac:dyDescent="0.2">
-      <c r="B35" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="13" t="e">
-        <f t="shared" ref="C35" si="19">+C24/C23</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D35" s="13" t="e">
-        <f t="shared" ref="D35:K35" si="20">+D24/D23</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E35" s="13">
-        <f t="shared" si="20"/>
-        <v>0.17602888605457423</v>
-      </c>
-      <c r="F35" s="13">
-        <f t="shared" si="20"/>
-        <v>-8.7428721306379313E-4</v>
-      </c>
-      <c r="G35" s="13">
-        <f t="shared" si="20"/>
-        <v>8.1146911811813591E-2</v>
-      </c>
-      <c r="H35" s="13">
-        <f t="shared" si="20"/>
-        <v>0.12164559432673341</v>
-      </c>
-      <c r="I35" s="13">
-        <f t="shared" si="20"/>
-        <v>0.1401339306143827</v>
-      </c>
-      <c r="J35" s="13">
-        <f t="shared" si="20"/>
-        <v>-0.28862876254180608</v>
-      </c>
-      <c r="K35" s="13">
-        <f t="shared" si="20"/>
-        <v>8.0454685488139055E-2</v>
-      </c>
-      <c r="L35" s="13">
-        <f>+L24/L23</f>
-        <v>0.29266328961052018</v>
-      </c>
-      <c r="M35" s="13">
-        <f>+M24/M23</f>
-        <v>0.17090384970470626</v>
-      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
       <c r="N35" s="7"/>
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
@@ -32158,91 +32524,91 @@
       <c r="GY156" s="3"/>
     </row>
     <row r="157" spans="3:207" x14ac:dyDescent="0.2">
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
-      <c r="I157" s="7"/>
-      <c r="J157" s="7"/>
-      <c r="K157" s="7"/>
-      <c r="L157" s="7"/>
-      <c r="M157" s="7"/>
-      <c r="N157" s="7"/>
-      <c r="O157" s="7"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="7"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="7"/>
-      <c r="T157" s="7"/>
-      <c r="U157" s="7"/>
-      <c r="V157" s="7"/>
-      <c r="W157" s="7"/>
-      <c r="X157" s="7"/>
-      <c r="Y157" s="7"/>
-      <c r="Z157" s="7"/>
-      <c r="AA157" s="7"/>
-      <c r="AB157" s="7"/>
-      <c r="AC157" s="7"/>
-      <c r="AD157" s="7"/>
-      <c r="AE157" s="7"/>
-      <c r="AF157" s="7"/>
-      <c r="AG157" s="7"/>
-      <c r="AH157" s="7"/>
-      <c r="AI157" s="7"/>
-      <c r="AJ157" s="7"/>
-      <c r="AK157" s="7"/>
-      <c r="AL157" s="7"/>
-      <c r="AM157" s="7"/>
-      <c r="AN157" s="7"/>
-      <c r="AO157" s="7"/>
-      <c r="AP157" s="7"/>
-      <c r="AQ157" s="7"/>
-      <c r="AR157" s="7"/>
-      <c r="AS157" s="7"/>
-      <c r="AT157" s="7"/>
-      <c r="AU157" s="7"/>
-      <c r="AV157" s="7"/>
-      <c r="AW157" s="7"/>
-      <c r="AX157" s="7"/>
-      <c r="AY157" s="7"/>
-      <c r="AZ157" s="7"/>
-      <c r="BA157" s="7"/>
-      <c r="BB157" s="7"/>
-      <c r="BC157" s="7"/>
-      <c r="BD157" s="7"/>
-      <c r="BE157" s="7"/>
-      <c r="BF157" s="7"/>
-      <c r="BG157" s="7"/>
-      <c r="BH157" s="7"/>
-      <c r="BI157" s="7"/>
-      <c r="BJ157" s="7"/>
-      <c r="BK157" s="7"/>
-      <c r="BL157" s="7"/>
-      <c r="BM157" s="7"/>
-      <c r="BN157" s="7"/>
-      <c r="BO157" s="7"/>
-      <c r="BP157" s="7"/>
-      <c r="BQ157" s="7"/>
-      <c r="BR157" s="7"/>
-      <c r="BS157" s="7"/>
-      <c r="BT157" s="7"/>
-      <c r="BU157" s="7"/>
-      <c r="BV157" s="7"/>
-      <c r="BW157" s="7"/>
-      <c r="BX157" s="7"/>
-      <c r="BY157" s="7"/>
-      <c r="BZ157" s="7"/>
-      <c r="CA157" s="7"/>
-      <c r="CB157" s="7"/>
-      <c r="CC157" s="7"/>
-      <c r="CD157" s="7"/>
-      <c r="CE157" s="7"/>
-      <c r="CF157" s="7"/>
-      <c r="CG157" s="7"/>
-      <c r="CH157" s="7"/>
-      <c r="CI157" s="7"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3"/>
+      <c r="L157" s="3"/>
+      <c r="M157" s="3"/>
+      <c r="N157" s="3"/>
+      <c r="O157" s="3"/>
+      <c r="P157" s="3"/>
+      <c r="Q157" s="3"/>
+      <c r="R157" s="3"/>
+      <c r="S157" s="3"/>
+      <c r="T157" s="3"/>
+      <c r="U157" s="3"/>
+      <c r="V157" s="3"/>
+      <c r="W157" s="3"/>
+      <c r="X157" s="3"/>
+      <c r="Y157" s="3"/>
+      <c r="Z157" s="3"/>
+      <c r="AA157" s="3"/>
+      <c r="AB157" s="3"/>
+      <c r="AC157" s="3"/>
+      <c r="AD157" s="3"/>
+      <c r="AE157" s="3"/>
+      <c r="AF157" s="3"/>
+      <c r="AG157" s="3"/>
+      <c r="AH157" s="3"/>
+      <c r="AI157" s="3"/>
+      <c r="AJ157" s="3"/>
+      <c r="AK157" s="3"/>
+      <c r="AL157" s="3"/>
+      <c r="AM157" s="3"/>
+      <c r="AN157" s="3"/>
+      <c r="AO157" s="3"/>
+      <c r="AP157" s="3"/>
+      <c r="AQ157" s="3"/>
+      <c r="AR157" s="3"/>
+      <c r="AS157" s="3"/>
+      <c r="AT157" s="3"/>
+      <c r="AU157" s="3"/>
+      <c r="AV157" s="3"/>
+      <c r="AW157" s="3"/>
+      <c r="AX157" s="3"/>
+      <c r="AY157" s="3"/>
+      <c r="AZ157" s="3"/>
+      <c r="BA157" s="3"/>
+      <c r="BB157" s="3"/>
+      <c r="BC157" s="3"/>
+      <c r="BD157" s="3"/>
+      <c r="BE157" s="3"/>
+      <c r="BF157" s="3"/>
+      <c r="BG157" s="3"/>
+      <c r="BH157" s="3"/>
+      <c r="BI157" s="3"/>
+      <c r="BJ157" s="3"/>
+      <c r="BK157" s="3"/>
+      <c r="BL157" s="3"/>
+      <c r="BM157" s="3"/>
+      <c r="BN157" s="3"/>
+      <c r="BO157" s="3"/>
+      <c r="BP157" s="3"/>
+      <c r="BQ157" s="3"/>
+      <c r="BR157" s="3"/>
+      <c r="BS157" s="3"/>
+      <c r="BT157" s="3"/>
+      <c r="BU157" s="3"/>
+      <c r="BV157" s="3"/>
+      <c r="BW157" s="3"/>
+      <c r="BX157" s="3"/>
+      <c r="BY157" s="3"/>
+      <c r="BZ157" s="3"/>
+      <c r="CA157" s="3"/>
+      <c r="CB157" s="3"/>
+      <c r="CC157" s="3"/>
+      <c r="CD157" s="3"/>
+      <c r="CE157" s="3"/>
+      <c r="CF157" s="3"/>
+      <c r="CG157" s="3"/>
+      <c r="CH157" s="3"/>
+      <c r="CI157" s="3"/>
       <c r="CJ157" s="3"/>
       <c r="CK157" s="3"/>
       <c r="CL157" s="3"/>
@@ -32365,91 +32731,91 @@
       <c r="GY157" s="3"/>
     </row>
     <row r="158" spans="3:207" x14ac:dyDescent="0.2">
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
-      <c r="H158" s="7"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
-      <c r="K158" s="7"/>
-      <c r="L158" s="7"/>
-      <c r="M158" s="7"/>
-      <c r="N158" s="7"/>
-      <c r="O158" s="7"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="7"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="7"/>
-      <c r="T158" s="7"/>
-      <c r="U158" s="7"/>
-      <c r="V158" s="7"/>
-      <c r="W158" s="7"/>
-      <c r="X158" s="7"/>
-      <c r="Y158" s="7"/>
-      <c r="Z158" s="7"/>
-      <c r="AA158" s="7"/>
-      <c r="AB158" s="7"/>
-      <c r="AC158" s="7"/>
-      <c r="AD158" s="7"/>
-      <c r="AE158" s="7"/>
-      <c r="AF158" s="7"/>
-      <c r="AG158" s="7"/>
-      <c r="AH158" s="7"/>
-      <c r="AI158" s="7"/>
-      <c r="AJ158" s="7"/>
-      <c r="AK158" s="7"/>
-      <c r="AL158" s="7"/>
-      <c r="AM158" s="7"/>
-      <c r="AN158" s="7"/>
-      <c r="AO158" s="7"/>
-      <c r="AP158" s="7"/>
-      <c r="AQ158" s="7"/>
-      <c r="AR158" s="7"/>
-      <c r="AS158" s="7"/>
-      <c r="AT158" s="7"/>
-      <c r="AU158" s="7"/>
-      <c r="AV158" s="7"/>
-      <c r="AW158" s="7"/>
-      <c r="AX158" s="7"/>
-      <c r="AY158" s="7"/>
-      <c r="AZ158" s="7"/>
-      <c r="BA158" s="7"/>
-      <c r="BB158" s="7"/>
-      <c r="BC158" s="7"/>
-      <c r="BD158" s="7"/>
-      <c r="BE158" s="7"/>
-      <c r="BF158" s="7"/>
-      <c r="BG158" s="7"/>
-      <c r="BH158" s="7"/>
-      <c r="BI158" s="7"/>
-      <c r="BJ158" s="7"/>
-      <c r="BK158" s="7"/>
-      <c r="BL158" s="7"/>
-      <c r="BM158" s="7"/>
-      <c r="BN158" s="7"/>
-      <c r="BO158" s="7"/>
-      <c r="BP158" s="7"/>
-      <c r="BQ158" s="7"/>
-      <c r="BR158" s="7"/>
-      <c r="BS158" s="7"/>
-      <c r="BT158" s="7"/>
-      <c r="BU158" s="7"/>
-      <c r="BV158" s="7"/>
-      <c r="BW158" s="7"/>
-      <c r="BX158" s="7"/>
-      <c r="BY158" s="7"/>
-      <c r="BZ158" s="7"/>
-      <c r="CA158" s="7"/>
-      <c r="CB158" s="7"/>
-      <c r="CC158" s="7"/>
-      <c r="CD158" s="7"/>
-      <c r="CE158" s="7"/>
-      <c r="CF158" s="7"/>
-      <c r="CG158" s="7"/>
-      <c r="CH158" s="7"/>
-      <c r="CI158" s="7"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="3"/>
+      <c r="K158" s="3"/>
+      <c r="L158" s="3"/>
+      <c r="M158" s="3"/>
+      <c r="N158" s="3"/>
+      <c r="O158" s="3"/>
+      <c r="P158" s="3"/>
+      <c r="Q158" s="3"/>
+      <c r="R158" s="3"/>
+      <c r="S158" s="3"/>
+      <c r="T158" s="3"/>
+      <c r="U158" s="3"/>
+      <c r="V158" s="3"/>
+      <c r="W158" s="3"/>
+      <c r="X158" s="3"/>
+      <c r="Y158" s="3"/>
+      <c r="Z158" s="3"/>
+      <c r="AA158" s="3"/>
+      <c r="AB158" s="3"/>
+      <c r="AC158" s="3"/>
+      <c r="AD158" s="3"/>
+      <c r="AE158" s="3"/>
+      <c r="AF158" s="3"/>
+      <c r="AG158" s="3"/>
+      <c r="AH158" s="3"/>
+      <c r="AI158" s="3"/>
+      <c r="AJ158" s="3"/>
+      <c r="AK158" s="3"/>
+      <c r="AL158" s="3"/>
+      <c r="AM158" s="3"/>
+      <c r="AN158" s="3"/>
+      <c r="AO158" s="3"/>
+      <c r="AP158" s="3"/>
+      <c r="AQ158" s="3"/>
+      <c r="AR158" s="3"/>
+      <c r="AS158" s="3"/>
+      <c r="AT158" s="3"/>
+      <c r="AU158" s="3"/>
+      <c r="AV158" s="3"/>
+      <c r="AW158" s="3"/>
+      <c r="AX158" s="3"/>
+      <c r="AY158" s="3"/>
+      <c r="AZ158" s="3"/>
+      <c r="BA158" s="3"/>
+      <c r="BB158" s="3"/>
+      <c r="BC158" s="3"/>
+      <c r="BD158" s="3"/>
+      <c r="BE158" s="3"/>
+      <c r="BF158" s="3"/>
+      <c r="BG158" s="3"/>
+      <c r="BH158" s="3"/>
+      <c r="BI158" s="3"/>
+      <c r="BJ158" s="3"/>
+      <c r="BK158" s="3"/>
+      <c r="BL158" s="3"/>
+      <c r="BM158" s="3"/>
+      <c r="BN158" s="3"/>
+      <c r="BO158" s="3"/>
+      <c r="BP158" s="3"/>
+      <c r="BQ158" s="3"/>
+      <c r="BR158" s="3"/>
+      <c r="BS158" s="3"/>
+      <c r="BT158" s="3"/>
+      <c r="BU158" s="3"/>
+      <c r="BV158" s="3"/>
+      <c r="BW158" s="3"/>
+      <c r="BX158" s="3"/>
+      <c r="BY158" s="3"/>
+      <c r="BZ158" s="3"/>
+      <c r="CA158" s="3"/>
+      <c r="CB158" s="3"/>
+      <c r="CC158" s="3"/>
+      <c r="CD158" s="3"/>
+      <c r="CE158" s="3"/>
+      <c r="CF158" s="3"/>
+      <c r="CG158" s="3"/>
+      <c r="CH158" s="3"/>
+      <c r="CI158" s="3"/>
       <c r="CJ158" s="3"/>
       <c r="CK158" s="3"/>
       <c r="CL158" s="3"/>
@@ -52029,420 +52395,6 @@
       <c r="GX252" s="3"/>
       <c r="GY252" s="3"/>
     </row>
-    <row r="253" spans="3:207" x14ac:dyDescent="0.2">
-      <c r="C253" s="3"/>
-      <c r="D253" s="3"/>
-      <c r="E253" s="3"/>
-      <c r="F253" s="3"/>
-      <c r="G253" s="3"/>
-      <c r="H253" s="3"/>
-      <c r="I253" s="3"/>
-      <c r="J253" s="3"/>
-      <c r="K253" s="3"/>
-      <c r="L253" s="3"/>
-      <c r="M253" s="3"/>
-      <c r="N253" s="3"/>
-      <c r="O253" s="3"/>
-      <c r="P253" s="3"/>
-      <c r="Q253" s="3"/>
-      <c r="R253" s="3"/>
-      <c r="S253" s="3"/>
-      <c r="T253" s="3"/>
-      <c r="U253" s="3"/>
-      <c r="V253" s="3"/>
-      <c r="W253" s="3"/>
-      <c r="X253" s="3"/>
-      <c r="Y253" s="3"/>
-      <c r="Z253" s="3"/>
-      <c r="AA253" s="3"/>
-      <c r="AB253" s="3"/>
-      <c r="AC253" s="3"/>
-      <c r="AD253" s="3"/>
-      <c r="AE253" s="3"/>
-      <c r="AF253" s="3"/>
-      <c r="AG253" s="3"/>
-      <c r="AH253" s="3"/>
-      <c r="AI253" s="3"/>
-      <c r="AJ253" s="3"/>
-      <c r="AK253" s="3"/>
-      <c r="AL253" s="3"/>
-      <c r="AM253" s="3"/>
-      <c r="AN253" s="3"/>
-      <c r="AO253" s="3"/>
-      <c r="AP253" s="3"/>
-      <c r="AQ253" s="3"/>
-      <c r="AR253" s="3"/>
-      <c r="AS253" s="3"/>
-      <c r="AT253" s="3"/>
-      <c r="AU253" s="3"/>
-      <c r="AV253" s="3"/>
-      <c r="AW253" s="3"/>
-      <c r="AX253" s="3"/>
-      <c r="AY253" s="3"/>
-      <c r="AZ253" s="3"/>
-      <c r="BA253" s="3"/>
-      <c r="BB253" s="3"/>
-      <c r="BC253" s="3"/>
-      <c r="BD253" s="3"/>
-      <c r="BE253" s="3"/>
-      <c r="BF253" s="3"/>
-      <c r="BG253" s="3"/>
-      <c r="BH253" s="3"/>
-      <c r="BI253" s="3"/>
-      <c r="BJ253" s="3"/>
-      <c r="BK253" s="3"/>
-      <c r="BL253" s="3"/>
-      <c r="BM253" s="3"/>
-      <c r="BN253" s="3"/>
-      <c r="BO253" s="3"/>
-      <c r="BP253" s="3"/>
-      <c r="BQ253" s="3"/>
-      <c r="BR253" s="3"/>
-      <c r="BS253" s="3"/>
-      <c r="BT253" s="3"/>
-      <c r="BU253" s="3"/>
-      <c r="BV253" s="3"/>
-      <c r="BW253" s="3"/>
-      <c r="BX253" s="3"/>
-      <c r="BY253" s="3"/>
-      <c r="BZ253" s="3"/>
-      <c r="CA253" s="3"/>
-      <c r="CB253" s="3"/>
-      <c r="CC253" s="3"/>
-      <c r="CD253" s="3"/>
-      <c r="CE253" s="3"/>
-      <c r="CF253" s="3"/>
-      <c r="CG253" s="3"/>
-      <c r="CH253" s="3"/>
-      <c r="CI253" s="3"/>
-      <c r="CJ253" s="3"/>
-      <c r="CK253" s="3"/>
-      <c r="CL253" s="3"/>
-      <c r="CM253" s="3"/>
-      <c r="CN253" s="3"/>
-      <c r="CO253" s="3"/>
-      <c r="CP253" s="3"/>
-      <c r="CQ253" s="3"/>
-      <c r="CR253" s="3"/>
-      <c r="CS253" s="3"/>
-      <c r="CT253" s="3"/>
-      <c r="CU253" s="3"/>
-      <c r="CV253" s="3"/>
-      <c r="CW253" s="3"/>
-      <c r="CX253" s="3"/>
-      <c r="CY253" s="3"/>
-      <c r="CZ253" s="3"/>
-      <c r="DA253" s="3"/>
-      <c r="DB253" s="3"/>
-      <c r="DC253" s="3"/>
-      <c r="DD253" s="3"/>
-      <c r="DE253" s="3"/>
-      <c r="DF253" s="3"/>
-      <c r="DG253" s="3"/>
-      <c r="DH253" s="3"/>
-      <c r="DI253" s="3"/>
-      <c r="DJ253" s="3"/>
-      <c r="DK253" s="3"/>
-      <c r="DL253" s="3"/>
-      <c r="DM253" s="3"/>
-      <c r="DN253" s="3"/>
-      <c r="DO253" s="3"/>
-      <c r="DP253" s="3"/>
-      <c r="DQ253" s="3"/>
-      <c r="DR253" s="3"/>
-      <c r="DS253" s="3"/>
-      <c r="DT253" s="3"/>
-      <c r="DU253" s="3"/>
-      <c r="DV253" s="3"/>
-      <c r="DW253" s="3"/>
-      <c r="DX253" s="3"/>
-      <c r="DY253" s="3"/>
-      <c r="DZ253" s="3"/>
-      <c r="EA253" s="3"/>
-      <c r="EB253" s="3"/>
-      <c r="EC253" s="3"/>
-      <c r="ED253" s="3"/>
-      <c r="EE253" s="3"/>
-      <c r="EF253" s="3"/>
-      <c r="EG253" s="3"/>
-      <c r="EH253" s="3"/>
-      <c r="EI253" s="3"/>
-      <c r="EJ253" s="3"/>
-      <c r="EK253" s="3"/>
-      <c r="EL253" s="3"/>
-      <c r="EM253" s="3"/>
-      <c r="EN253" s="3"/>
-      <c r="EO253" s="3"/>
-      <c r="EP253" s="3"/>
-      <c r="EQ253" s="3"/>
-      <c r="ER253" s="3"/>
-      <c r="ES253" s="3"/>
-      <c r="ET253" s="3"/>
-      <c r="EU253" s="3"/>
-      <c r="EV253" s="3"/>
-      <c r="EW253" s="3"/>
-      <c r="EX253" s="3"/>
-      <c r="EY253" s="3"/>
-      <c r="EZ253" s="3"/>
-      <c r="FA253" s="3"/>
-      <c r="FB253" s="3"/>
-      <c r="FC253" s="3"/>
-      <c r="FD253" s="3"/>
-      <c r="FE253" s="3"/>
-      <c r="FF253" s="3"/>
-      <c r="FG253" s="3"/>
-      <c r="FH253" s="3"/>
-      <c r="FI253" s="3"/>
-      <c r="FJ253" s="3"/>
-      <c r="FK253" s="3"/>
-      <c r="FL253" s="3"/>
-      <c r="FM253" s="3"/>
-      <c r="FN253" s="3"/>
-      <c r="FO253" s="3"/>
-      <c r="FP253" s="3"/>
-      <c r="FQ253" s="3"/>
-      <c r="FR253" s="3"/>
-      <c r="FS253" s="3"/>
-      <c r="FT253" s="3"/>
-      <c r="FU253" s="3"/>
-      <c r="FV253" s="3"/>
-      <c r="FW253" s="3"/>
-      <c r="FX253" s="3"/>
-      <c r="FY253" s="3"/>
-      <c r="FZ253" s="3"/>
-      <c r="GA253" s="3"/>
-      <c r="GB253" s="3"/>
-      <c r="GC253" s="3"/>
-      <c r="GD253" s="3"/>
-      <c r="GE253" s="3"/>
-      <c r="GF253" s="3"/>
-      <c r="GG253" s="3"/>
-      <c r="GH253" s="3"/>
-      <c r="GI253" s="3"/>
-      <c r="GJ253" s="3"/>
-      <c r="GK253" s="3"/>
-      <c r="GL253" s="3"/>
-      <c r="GM253" s="3"/>
-      <c r="GN253" s="3"/>
-      <c r="GO253" s="3"/>
-      <c r="GP253" s="3"/>
-      <c r="GQ253" s="3"/>
-      <c r="GR253" s="3"/>
-      <c r="GS253" s="3"/>
-      <c r="GT253" s="3"/>
-      <c r="GU253" s="3"/>
-      <c r="GV253" s="3"/>
-      <c r="GW253" s="3"/>
-      <c r="GX253" s="3"/>
-      <c r="GY253" s="3"/>
-    </row>
-    <row r="254" spans="3:207" x14ac:dyDescent="0.2">
-      <c r="C254" s="3"/>
-      <c r="D254" s="3"/>
-      <c r="E254" s="3"/>
-      <c r="F254" s="3"/>
-      <c r="G254" s="3"/>
-      <c r="H254" s="3"/>
-      <c r="I254" s="3"/>
-      <c r="J254" s="3"/>
-      <c r="K254" s="3"/>
-      <c r="L254" s="3"/>
-      <c r="M254" s="3"/>
-      <c r="N254" s="3"/>
-      <c r="O254" s="3"/>
-      <c r="P254" s="3"/>
-      <c r="Q254" s="3"/>
-      <c r="R254" s="3"/>
-      <c r="S254" s="3"/>
-      <c r="T254" s="3"/>
-      <c r="U254" s="3"/>
-      <c r="V254" s="3"/>
-      <c r="W254" s="3"/>
-      <c r="X254" s="3"/>
-      <c r="Y254" s="3"/>
-      <c r="Z254" s="3"/>
-      <c r="AA254" s="3"/>
-      <c r="AB254" s="3"/>
-      <c r="AC254" s="3"/>
-      <c r="AD254" s="3"/>
-      <c r="AE254" s="3"/>
-      <c r="AF254" s="3"/>
-      <c r="AG254" s="3"/>
-      <c r="AH254" s="3"/>
-      <c r="AI254" s="3"/>
-      <c r="AJ254" s="3"/>
-      <c r="AK254" s="3"/>
-      <c r="AL254" s="3"/>
-      <c r="AM254" s="3"/>
-      <c r="AN254" s="3"/>
-      <c r="AO254" s="3"/>
-      <c r="AP254" s="3"/>
-      <c r="AQ254" s="3"/>
-      <c r="AR254" s="3"/>
-      <c r="AS254" s="3"/>
-      <c r="AT254" s="3"/>
-      <c r="AU254" s="3"/>
-      <c r="AV254" s="3"/>
-      <c r="AW254" s="3"/>
-      <c r="AX254" s="3"/>
-      <c r="AY254" s="3"/>
-      <c r="AZ254" s="3"/>
-      <c r="BA254" s="3"/>
-      <c r="BB254" s="3"/>
-      <c r="BC254" s="3"/>
-      <c r="BD254" s="3"/>
-      <c r="BE254" s="3"/>
-      <c r="BF254" s="3"/>
-      <c r="BG254" s="3"/>
-      <c r="BH254" s="3"/>
-      <c r="BI254" s="3"/>
-      <c r="BJ254" s="3"/>
-      <c r="BK254" s="3"/>
-      <c r="BL254" s="3"/>
-      <c r="BM254" s="3"/>
-      <c r="BN254" s="3"/>
-      <c r="BO254" s="3"/>
-      <c r="BP254" s="3"/>
-      <c r="BQ254" s="3"/>
-      <c r="BR254" s="3"/>
-      <c r="BS254" s="3"/>
-      <c r="BT254" s="3"/>
-      <c r="BU254" s="3"/>
-      <c r="BV254" s="3"/>
-      <c r="BW254" s="3"/>
-      <c r="BX254" s="3"/>
-      <c r="BY254" s="3"/>
-      <c r="BZ254" s="3"/>
-      <c r="CA254" s="3"/>
-      <c r="CB254" s="3"/>
-      <c r="CC254" s="3"/>
-      <c r="CD254" s="3"/>
-      <c r="CE254" s="3"/>
-      <c r="CF254" s="3"/>
-      <c r="CG254" s="3"/>
-      <c r="CH254" s="3"/>
-      <c r="CI254" s="3"/>
-      <c r="CJ254" s="3"/>
-      <c r="CK254" s="3"/>
-      <c r="CL254" s="3"/>
-      <c r="CM254" s="3"/>
-      <c r="CN254" s="3"/>
-      <c r="CO254" s="3"/>
-      <c r="CP254" s="3"/>
-      <c r="CQ254" s="3"/>
-      <c r="CR254" s="3"/>
-      <c r="CS254" s="3"/>
-      <c r="CT254" s="3"/>
-      <c r="CU254" s="3"/>
-      <c r="CV254" s="3"/>
-      <c r="CW254" s="3"/>
-      <c r="CX254" s="3"/>
-      <c r="CY254" s="3"/>
-      <c r="CZ254" s="3"/>
-      <c r="DA254" s="3"/>
-      <c r="DB254" s="3"/>
-      <c r="DC254" s="3"/>
-      <c r="DD254" s="3"/>
-      <c r="DE254" s="3"/>
-      <c r="DF254" s="3"/>
-      <c r="DG254" s="3"/>
-      <c r="DH254" s="3"/>
-      <c r="DI254" s="3"/>
-      <c r="DJ254" s="3"/>
-      <c r="DK254" s="3"/>
-      <c r="DL254" s="3"/>
-      <c r="DM254" s="3"/>
-      <c r="DN254" s="3"/>
-      <c r="DO254" s="3"/>
-      <c r="DP254" s="3"/>
-      <c r="DQ254" s="3"/>
-      <c r="DR254" s="3"/>
-      <c r="DS254" s="3"/>
-      <c r="DT254" s="3"/>
-      <c r="DU254" s="3"/>
-      <c r="DV254" s="3"/>
-      <c r="DW254" s="3"/>
-      <c r="DX254" s="3"/>
-      <c r="DY254" s="3"/>
-      <c r="DZ254" s="3"/>
-      <c r="EA254" s="3"/>
-      <c r="EB254" s="3"/>
-      <c r="EC254" s="3"/>
-      <c r="ED254" s="3"/>
-      <c r="EE254" s="3"/>
-      <c r="EF254" s="3"/>
-      <c r="EG254" s="3"/>
-      <c r="EH254" s="3"/>
-      <c r="EI254" s="3"/>
-      <c r="EJ254" s="3"/>
-      <c r="EK254" s="3"/>
-      <c r="EL254" s="3"/>
-      <c r="EM254" s="3"/>
-      <c r="EN254" s="3"/>
-      <c r="EO254" s="3"/>
-      <c r="EP254" s="3"/>
-      <c r="EQ254" s="3"/>
-      <c r="ER254" s="3"/>
-      <c r="ES254" s="3"/>
-      <c r="ET254" s="3"/>
-      <c r="EU254" s="3"/>
-      <c r="EV254" s="3"/>
-      <c r="EW254" s="3"/>
-      <c r="EX254" s="3"/>
-      <c r="EY254" s="3"/>
-      <c r="EZ254" s="3"/>
-      <c r="FA254" s="3"/>
-      <c r="FB254" s="3"/>
-      <c r="FC254" s="3"/>
-      <c r="FD254" s="3"/>
-      <c r="FE254" s="3"/>
-      <c r="FF254" s="3"/>
-      <c r="FG254" s="3"/>
-      <c r="FH254" s="3"/>
-      <c r="FI254" s="3"/>
-      <c r="FJ254" s="3"/>
-      <c r="FK254" s="3"/>
-      <c r="FL254" s="3"/>
-      <c r="FM254" s="3"/>
-      <c r="FN254" s="3"/>
-      <c r="FO254" s="3"/>
-      <c r="FP254" s="3"/>
-      <c r="FQ254" s="3"/>
-      <c r="FR254" s="3"/>
-      <c r="FS254" s="3"/>
-      <c r="FT254" s="3"/>
-      <c r="FU254" s="3"/>
-      <c r="FV254" s="3"/>
-      <c r="FW254" s="3"/>
-      <c r="FX254" s="3"/>
-      <c r="FY254" s="3"/>
-      <c r="FZ254" s="3"/>
-      <c r="GA254" s="3"/>
-      <c r="GB254" s="3"/>
-      <c r="GC254" s="3"/>
-      <c r="GD254" s="3"/>
-      <c r="GE254" s="3"/>
-      <c r="GF254" s="3"/>
-      <c r="GG254" s="3"/>
-      <c r="GH254" s="3"/>
-      <c r="GI254" s="3"/>
-      <c r="GJ254" s="3"/>
-      <c r="GK254" s="3"/>
-      <c r="GL254" s="3"/>
-      <c r="GM254" s="3"/>
-      <c r="GN254" s="3"/>
-      <c r="GO254" s="3"/>
-      <c r="GP254" s="3"/>
-      <c r="GQ254" s="3"/>
-      <c r="GR254" s="3"/>
-      <c r="GS254" s="3"/>
-      <c r="GT254" s="3"/>
-      <c r="GU254" s="3"/>
-      <c r="GV254" s="3"/>
-      <c r="GW254" s="3"/>
-      <c r="GX254" s="3"/>
-      <c r="GY254" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{F19B80C1-46AF-4099-8AA5-CF7124DDE498}"/>
